--- a/docs/project_day_tracker.xlsx
+++ b/docs/project_day_tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8210ae7fbd0021b7/CVs/Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8210ae7fbd0021b7/CVs/Project/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EFE3BC5-529E-478F-AF14-F0795EAFA0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{0EFE3BC5-529E-478F-AF14-F0795EAFA0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E0BAB5C-AE3D-4182-B667-2B03906445E3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="87">
   <si>
     <t>30-Minute-Per-Day Project Logger &amp; Tracker</t>
   </si>
@@ -244,6 +244,57 @@
   </si>
   <si>
     <t>7. Recommended habit: at the end of each session, write one note on what to do next tomorrow.</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Created project folder structure, made README.md and requirements.txt, created GitHub repo, linked local project to GitHub, completed first push successfully.</t>
+  </si>
+  <si>
+    <t>Project structure created and GitHub repo connected successfully.</t>
+  </si>
+  <si>
+    <t>Saved Online Retail.csv into the data folder and confirmed the file path for the project workflow.</t>
+  </si>
+  <si>
+    <t>Raw dataset saved in data/Online Retail.csv.</t>
+  </si>
+  <si>
+    <t>Created virtual environment, activated it, installed pandas, created src/explore_data.py, and successfully loaded the dataset in Python.</t>
+  </si>
+  <si>
+    <t>explore_data.py ran successfully and printed dataset shape, columns, data types, missing values, and first 10 rows.</t>
+  </si>
+  <si>
+    <t>Reviewed dataset issues from Python output. Identified missing Description and CustomerID values, date stored as text, cancellations/returns indicators, duplicate rows, and pricing anomalies to address in cleaning.</t>
+  </si>
+  <si>
+    <t>Main data cleaning issues identified and ready for clean_data.py stage.</t>
+  </si>
+  <si>
+    <t>Defined the project business goal, problem statement, and core KPI list. Confirmed the project focus is building a clean retail KPI reporting workflow for sales, orders, cancellations, customer coverage, and product/country analysis.</t>
+  </si>
+  <si>
+    <t>Business goal, problem statement, and KPI list finalised in README.md.</t>
+  </si>
+  <si>
+    <t>Created the first version of clean_data.py. Loaded the raw CSV, converted InvoiceDate to datetime format, created a Revenue column, and saved the first cleaned dataset output.</t>
+  </si>
+  <si>
+    <t>Initial cleaned dataset created as data/cleaned_online_retail.csv with parsed dates and Revenue column.</t>
+  </si>
+  <si>
+    <t>Confirmed the first cleaned output file was created and committed the latest project progress to GitHub, including the KPI definitions and the initial data cleaning script.</t>
+  </si>
+  <si>
+    <t>Initial cleaning milestone saved to GitHub with clean_data.py and updated README.md.</t>
+  </si>
+  <si>
+    <t>Extended clean_data.py by creating an IsCancelled flag based on invoice numbers starting with C. Generated two outputs: a full cleaned working file and a sales-only cleaned dataset excluding cancelled rows for core KPI analysis.</t>
+  </si>
+  <si>
+    <t>Created cleaned_online_retail.csv and cleaned_online_retail_sales_only.csv with cancellation handling applied.</t>
   </si>
 </sst>
 </file>
@@ -455,6 +506,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,14 +836,14 @@
       </c>
       <c r="F2" s="4">
         <f>COUNTIF(E10:E44,"Completed")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="19" t="str">
         <f>REPT("█",ROUND(F3*20,0))&amp;REPT("░",20-ROUND(F3*20,0))</f>
-        <v>░░░░░░░░░░░░░░░░░░░░</v>
+        <v>█████░░░░░░░░░░░░░░░</v>
       </c>
       <c r="J2" s="17"/>
     </row>
@@ -804,7 +859,7 @@
       </c>
       <c r="F3" s="6">
         <f>IF(B5=0,0,F2/B5)</f>
-        <v>0</v>
+        <v>0.22857142857142856</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -819,7 +874,7 @@
       </c>
       <c r="F4" s="4">
         <f>SUM(F10:F44)</f>
-        <v>0</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -834,7 +889,7 @@
       </c>
       <c r="F5" s="4">
         <f>MAX(B5-F2,0)</f>
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -851,7 +906,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
@@ -899,19 +954,25 @@
         <v>23</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F10" s="11">
+        <v>30</v>
+      </c>
       <c r="G10" s="8" t="str">
         <f t="shared" ref="G10:G44" si="2">IF(OR(E10="In Progress",E10="Completed",F10&gt;0),"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H10" s="8" t="str">
         <f t="shared" ref="H10:H44" si="3">IF(E10="Completed","Yes","No")</f>
-        <v>No</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
@@ -929,19 +990,25 @@
         <v>25</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F11" s="11">
+        <v>30</v>
+      </c>
       <c r="G11" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H11" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
@@ -959,19 +1026,25 @@
         <v>26</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F12" s="11">
+        <v>45</v>
+      </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H12" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
@@ -989,19 +1062,25 @@
         <v>27</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F13" s="11">
+        <v>30</v>
+      </c>
       <c r="G13" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H13" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
@@ -1019,19 +1098,25 @@
         <v>28</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F14" s="11">
+        <v>30</v>
+      </c>
       <c r="G14" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H14" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I14" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
@@ -1049,19 +1134,25 @@
         <v>29</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F15" s="11">
+        <v>30</v>
+      </c>
       <c r="G15" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H15" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
@@ -1079,19 +1170,25 @@
         <v>30</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F16" s="11">
+        <v>20</v>
+      </c>
       <c r="G16" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H16" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
@@ -1109,19 +1206,25 @@
         <v>31</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="F17" s="11">
+        <v>30</v>
+      </c>
       <c r="G17" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="H17" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
+        <v>Yes</v>
+      </c>
+      <c r="I17" t="s">
+        <v>85</v>
+      </c>
+      <c r="J17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
@@ -1181,7 +1284,9 @@
         <v>No</v>
       </c>
       <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="J19" s="10">
+        <v>30</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
@@ -1972,15 +2077,15 @@
       </c>
       <c r="C49">
         <f>COUNTIFS($C$10:$C$44,A49,$E$10:$E$44,"Completed")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D49" s="13">
         <f>C49/B49</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <f>SUMIFS($F$10:$F$44,$C$10:$C$44,A49)</f>
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -1992,15 +2097,15 @@
       </c>
       <c r="C50">
         <f>COUNTIFS($C$10:$C$44,A50,$E$10:$E$44,"Completed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="13">
         <f>C50/B50</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E50">
         <f>SUMIFS($F$10:$F$44,$C$10:$C$44,A50)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -2092,6 +2197,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
